--- a/out/Attention-mamba2_repeat_2_000005.xlsx
+++ b/out/Attention-mamba2_repeat_2_000005.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.40535882480514</v>
+        <v>5.934848009080797</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.40535882480514</v>
+        <v>5.934848009080797</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.01436208449146875</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.01436208449146875</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>2.073179781458245</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.8053588248051395</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>2.073179781458245</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>2.073179781458245</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.8053588248051395</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>2.073179781458245</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>2.073179781458245</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.8053588248051395</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.40535882480514</v>
+        <v>6.534848009080797</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.40535882480514</v>
+        <v>6.534848009080797</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.01436208449146875</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.473179781458245</v>
+        <v>-0.01436208449146875</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>2.073179781458245</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.8053588248051395</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.073179781458245</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.073179781458245</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>2.073179781458245</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.073179781458245</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.073179781458245</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.073179781458245</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,14 +35917,14 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.073179781458245</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36712,14 +36712,14 @@
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.073179781458245</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37507,14 +37507,14 @@
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>2.073179781458245</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38302,14 +38302,14 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.473179781458245</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39097,14 +39097,14 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.473179781458245</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39892,14 +39892,14 @@
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.473179781458245</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40687,14 +40687,14 @@
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.473179781458245</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41482,14 +41482,14 @@
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.473179781458245</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42277,14 +42277,14 @@
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.473179781458245</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43072,14 +43072,14 @@
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.473179781458245</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43867,14 +43867,14 @@
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.473179781458245</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44662,14 +44662,14 @@
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.473179781458245</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45457,14 +45457,14 @@
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.473179781458245</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46259,7 +46259,7 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47047,14 +47047,14 @@
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.473179781458245</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47842,14 +47842,14 @@
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.473179781458245</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48637,14 +48637,14 @@
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>2.073179781458245</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49432,14 +49432,14 @@
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>2.073179781458245</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50227,14 +50227,14 @@
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>2.073179781458245</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51022,14 +51022,14 @@
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>2.073179781458245</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51817,14 +51817,14 @@
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>2.073179781458245</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52612,14 +52612,14 @@
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>2.073179781458245</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53407,14 +53407,14 @@
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>2.073179781458245</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54202,14 +54202,14 @@
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.473179781458245</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -54997,14 +54997,14 @@
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>1.473179781458245</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55792,14 +55792,14 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>1.473179781458245</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56587,14 +56587,14 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>1.473179781458245</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57382,14 +57382,14 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>1.473179781458245</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58177,14 +58177,14 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>1.473179781458245</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58972,14 +58972,14 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>1.473179781458245</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59774,7 +59774,7 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60569,7 +60569,7 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61364,7 +61364,7 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62159,7 +62159,7 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62954,7 +62954,7 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63749,7 +63749,7 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64544,7 +64544,7 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65339,7 +65339,7 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66134,7 +66134,7 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66929,7 +66929,7 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67724,7 +67724,7 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68519,7 +68519,7 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69314,7 +69314,7 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70102,14 +70102,14 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>2.073179781458245</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70904,7 +70904,7 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.8053588248051395</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71699,7 +71699,7 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.8053588248051395</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72494,7 +72494,7 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73289,7 +73289,7 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74084,7 +74084,7 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74879,7 +74879,7 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75674,7 +75674,7 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76469,7 +76469,7 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77264,7 +77264,7 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78059,7 +78059,7 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78854,7 +78854,7 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79649,7 +79649,7 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80444,7 +80444,7 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81239,7 +81239,7 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82034,7 +82034,7 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82829,7 +82829,7 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83624,7 +83624,7 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84419,7 +84419,7 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85214,7 +85214,7 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86009,7 +86009,7 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86804,7 +86804,7 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87599,7 +87599,7 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88394,7 +88394,7 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89182,14 +89182,14 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>2.073179781458245</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89977,14 +89977,14 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>2.073179781458245</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90772,14 +90772,14 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>2.073179781458245</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91574,7 +91574,7 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.8053588248051395</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92362,14 +92362,14 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.8053588248051395</v>
+        <v>6.534848009080797</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93157,14 +93157,14 @@
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA116" t="n">
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.01436208449146875</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93952,14 +93952,14 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA117" t="n">
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.01436208449146875</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94754,7 +94754,7 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95549,7 +95549,7 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96337,14 +96337,14 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>1.473179781458245</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97132,14 +97132,14 @@
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>2.073179781458245</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97934,7 +97934,7 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.8053588248051395</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98729,7 +98729,7 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.8053588248051395</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99524,7 +99524,7 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.6143620844914688</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100312,14 +100312,14 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.40535882480514</v>
+        <v>6.534848009080797</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101107,14 +101107,14 @@
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA126" t="n">
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.01436208449146875</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/Attention-mamba2_repeat_2_000005.xlsx
+++ b/out/Attention-mamba2_repeat_2_000005.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.40535882480514</v>
+        <v>0.05999134442239212</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>2.073179781458245</v>
+        <v>0.05999134442239212</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.8053588248051395</v>
+        <v>0.7179430258540229</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>2.073179781458245</v>
+        <v>0.7179430258540229</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>2.073179781458245</v>
+        <v>0.7179430258540229</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.8053588248051395</v>
+        <v>0.7179430258540228</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>2.073179781458245</v>
+        <v>0.7179430258540228</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>2.073179781458245</v>
+        <v>0.7179430258540228</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.8053588248051395</v>
+        <v>0.05999134442239207</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.140008655577608</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.473179781458245</v>
+        <v>0.5179430258540227</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>2.073179781458245</v>
+        <v>0.7179430258540228</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.8053588248051395</v>
+        <v>0.7179430258540229</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.073179781458245</v>
+        <v>0.7179430258540229</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.073179781458245</v>
+        <v>1.375894707285654</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>2.073179781458245</v>
+        <v>1.375894707285654</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.073179781458245</v>
+        <v>1.375894707285654</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.073179781458245</v>
+        <v>1.375894707285654</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.073179781458245</v>
+        <v>1.375894707285654</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.073179781458245</v>
+        <v>1.375894707285654</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,7 +36719,7 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.073179781458245</v>
+        <v>1.375894707285654</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37514,7 +37514,7 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>2.073179781458245</v>
+        <v>1.375894707285654</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38309,7 +38309,7 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.473179781458245</v>
+        <v>1.375894707285654</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39104,7 +39104,7 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.473179781458245</v>
+        <v>1.175894707285654</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39899,7 +39899,7 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.473179781458245</v>
+        <v>1.175894707285654</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40694,7 +40694,7 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.473179781458245</v>
+        <v>1.175894707285654</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41489,7 +41489,7 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.473179781458245</v>
+        <v>1.175894707285654</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42284,7 +42284,7 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.473179781458245</v>
+        <v>1.175894707285654</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43079,7 +43079,7 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.473179781458245</v>
+        <v>1.175894707285654</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43874,7 +43874,7 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.473179781458245</v>
+        <v>1.175894707285654</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44669,7 +44669,7 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.473179781458245</v>
+        <v>1.175894707285654</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45464,7 +45464,7 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.473179781458245</v>
+        <v>0.5179430258540229</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46252,14 +46252,14 @@
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA57" t="n">
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.40535882480514</v>
+        <v>0.517943025854023</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47054,7 +47054,7 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.473179781458245</v>
+        <v>0.517943025854023</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47849,7 +47849,7 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.473179781458245</v>
+        <v>1.175894707285654</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48644,7 +48644,7 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>2.073179781458245</v>
+        <v>1.175894707285654</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49439,7 +49439,7 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>2.073179781458245</v>
+        <v>1.375894707285654</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50234,7 +50234,7 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>2.073179781458245</v>
+        <v>1.375894707285654</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51029,7 +51029,7 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>2.073179781458245</v>
+        <v>1.375894707285654</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51824,7 +51824,7 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>2.073179781458245</v>
+        <v>1.375894707285654</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52619,7 +52619,7 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>2.073179781458245</v>
+        <v>1.375894707285654</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53414,7 +53414,7 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>2.073179781458245</v>
+        <v>1.375894707285654</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54209,7 +54209,7 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.473179781458245</v>
+        <v>1.375894707285654</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -55004,7 +55004,7 @@
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>1.473179781458245</v>
+        <v>1.175894707285654</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55799,7 +55799,7 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>1.473179781458245</v>
+        <v>1.175894707285654</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56594,7 +56594,7 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>1.473179781458245</v>
+        <v>1.175894707285654</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57389,7 +57389,7 @@
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>1.473179781458245</v>
+        <v>1.175894707285654</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58184,7 +58184,7 @@
         <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>1.473179781458245</v>
+        <v>1.175894707285654</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58979,7 +58979,7 @@
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>1.473179781458245</v>
+        <v>0.5179430258540231</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59767,14 +59767,14 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA74" t="n">
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.1400086555776078</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60569,7 +60569,7 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61364,7 +61364,7 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62159,7 +62159,7 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62954,7 +62954,7 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63749,7 +63749,7 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64544,7 +64544,7 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65339,7 +65339,7 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66134,7 +66134,7 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66929,7 +66929,7 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67724,7 +67724,7 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68519,7 +68519,7 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69314,7 +69314,7 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.40535882480514</v>
+        <v>0.05999134442239212</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70102,14 +70102,14 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA87" t="n">
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>2.073179781458245</v>
+        <v>0.05999134442239218</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70904,7 +70904,7 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.8053588248051395</v>
+        <v>0.05999134442239218</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71699,7 +71699,7 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.8053588248051395</v>
+        <v>-0.5979603370092387</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72494,7 +72494,7 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.5979603370092387</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73289,7 +73289,7 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74084,7 +74084,7 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74879,7 +74879,7 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75674,7 +75674,7 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76469,7 +76469,7 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77264,7 +77264,7 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78059,7 +78059,7 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78854,7 +78854,7 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79649,7 +79649,7 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80444,7 +80444,7 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81239,7 +81239,7 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82034,7 +82034,7 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82829,7 +82829,7 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83624,7 +83624,7 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84419,7 +84419,7 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85214,7 +85214,7 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86009,7 +86009,7 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86804,7 +86804,7 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87599,7 +87599,7 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88394,7 +88394,7 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.40535882480514</v>
+        <v>0.05999134442239212</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89189,7 +89189,7 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>2.073179781458245</v>
+        <v>0.7179430258540229</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89984,7 +89984,7 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>2.073179781458245</v>
+        <v>1.375894707285654</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90779,7 +90779,7 @@
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>2.073179781458245</v>
+        <v>0.7179430258540229</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91574,7 +91574,7 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.8053588248051395</v>
+        <v>0.05999134442239219</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92369,7 +92369,7 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.8053588248051395</v>
+        <v>-0.5979603370092387</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93164,7 +93164,7 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93959,7 +93959,7 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94754,7 +94754,7 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95542,14 +95542,14 @@
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA119" t="n">
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.1400086555776078</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96344,7 +96344,7 @@
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>1.473179781458245</v>
+        <v>0.5179430258540229</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97139,7 +97139,7 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>2.073179781458245</v>
+        <v>0.7179430258540229</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97934,7 +97934,7 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.8053588248051395</v>
+        <v>0.05999134442239229</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98729,7 +98729,7 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.8053588248051395</v>
+        <v>-0.5979603370092387</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99524,7 +99524,7 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100319,7 +100319,7 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101114,7 +101114,7 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.40535882480514</v>
+        <v>-0.7979603370092387</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/Attention-mamba2_repeat_2_000005.xlsx
+++ b/out/Attention-mamba2_repeat_2_000005.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.2505265474319458</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.7979603370092387</v>
+        <v>-1.28</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.3352601230144501</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.7979603370092387</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.2300024777650833</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.7979603370092387</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.2636118829250336</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.7979603370092387</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.1085541546344757</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.7979603370092387</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.1176963448524475</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.7979603370092387</v>
+        <v>-0.16</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.197364404797554</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.7979603370092387</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.09499486535787582</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.7979603370092387</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.02549728006124496</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.7979603370092387</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.04874556511640549</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.7979603370092387</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.03663502261042595</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.7979603370092387</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.03518557548522949</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.7979603370092387</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.01470459252595901</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.7979603370092387</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.03903701156377792</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.7979603370092387</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.04322099685668945</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.7979603370092387</v>
+        <v>-0.3</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.2502374649047852</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.7979603370092387</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.2092070430517197</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.7979603370092387</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.4126845598220825</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.7979603370092387</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.3702339231967926</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.7979603370092387</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.3430816829204559</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.7979603370092387</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.4450112581253052</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.7979603370092387</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.3133969306945801</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.05999134442239212</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.04055844247341156</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.05999134442239212</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>-0.07518091797828674</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.7179430258540229</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.04308973252773285</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.7179430258540229</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.02594505250453949</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.7179430258540229</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.1699343621730804</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.7179430258540228</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.0428541898727417</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.7179430258540228</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.02365453541278839</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.7179430258540228</v>
+        <v>0.3</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.02728001400828362</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.05999134442239207</v>
+        <v>-0.3</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.3192705512046814</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.7979603370092387</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.413053035736084</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.7979603370092387</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.4840645492076874</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.140008655577608</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.001906275749206543</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.5179430258540227</v>
+        <v>-0.3</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.06062937527894974</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.7179430258540228</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>-0.05491506308317184</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.7179430258540229</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.03889298439025879</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.7179430258540229</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.04870113730430603</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.375894707285654</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.03293269872665405</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.375894707285654</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.03771161288022995</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.375894707285654</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.01879118382930756</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.375894707285654</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.04348297417163849</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.375894707285654</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.04798171669244766</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.375894707285654</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,10 +36716,10 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.03686877340078354</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.375894707285654</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37511,10 +37511,10 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.0449666753411293</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.375894707285654</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38306,10 +38306,10 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.04705824702978134</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.375894707285654</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39101,10 +39101,10 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.03792746365070343</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.175894707285654</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39896,10 +39896,10 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.04934027791023254</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.175894707285654</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40691,10 +40691,10 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.03827935457229614</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.175894707285654</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41486,10 +41486,10 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.04643064737319946</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.175894707285654</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42281,10 +42281,10 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.03216800093650818</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.175894707285654</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43076,10 +43076,10 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.04327747225761414</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.175894707285654</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43871,10 +43871,10 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.04913093149662018</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.175894707285654</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44666,10 +44666,10 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.02941092103719711</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.175894707285654</v>
+        <v>-0.16</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45461,10 +45461,10 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.05405247211456299</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.5179430258540229</v>
+        <v>-0.3</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46256,10 +46256,10 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.103893481194973</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.517943025854023</v>
+        <v>-0.3</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47051,10 +47051,10 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.03998608887195587</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.517943025854023</v>
+        <v>-0.16</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47846,10 +47846,10 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.01781599223613739</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.175894707285654</v>
+        <v>-0.16</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48641,10 +48641,10 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.03259295225143433</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.175894707285654</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49436,10 +49436,10 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.0571846216917038</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.375894707285654</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50231,10 +50231,10 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.004745960235595703</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.375894707285654</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51026,10 +51026,10 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.04522063583135605</v>
       </c>
       <c r="JB63" t="n">
-        <v>1.375894707285654</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51821,10 +51821,10 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.04015333205461502</v>
       </c>
       <c r="JB64" t="n">
-        <v>1.375894707285654</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52616,10 +52616,10 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.03893821686506271</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.375894707285654</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53411,10 +53411,10 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.04288101941347122</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.375894707285654</v>
+        <v>-0.16</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54206,10 +54206,10 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.04063998907804489</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.375894707285654</v>
+        <v>-0.16</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -55001,10 +55001,10 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.04287440329790115</v>
       </c>
       <c r="JB68" t="n">
-        <v>1.175894707285654</v>
+        <v>-0.16</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55796,10 +55796,10 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.0464266911149025</v>
       </c>
       <c r="JB69" t="n">
-        <v>1.175894707285654</v>
+        <v>-0.16</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56591,10 +56591,10 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.04280437529087067</v>
       </c>
       <c r="JB70" t="n">
-        <v>1.175894707285654</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57386,10 +57386,10 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0.04207804799079895</v>
       </c>
       <c r="JB71" t="n">
-        <v>1.175894707285654</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58181,10 +58181,10 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0.04846125096082687</v>
       </c>
       <c r="JB72" t="n">
-        <v>1.175894707285654</v>
+        <v>-0.3</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58972,14 +58972,14 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0.0273762047290802</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.5179430258540231</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59767,14 +59767,14 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.423413097858429</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.1400086555776078</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60566,10 +60566,10 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.425064891576767</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.7979603370092387</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61361,10 +61361,10 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.4135252237319946</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.7979603370092387</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62156,10 +62156,10 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.4389397799968719</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.7979603370092387</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62951,10 +62951,10 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.4556145370006561</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.7979603370092387</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63746,10 +63746,10 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.302689790725708</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.7979603370092387</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64541,10 +64541,10 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.2675372958183289</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.7979603370092387</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65336,10 +65336,10 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.2548133730888367</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.7979603370092387</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66131,10 +66131,10 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.3033689856529236</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.7979603370092387</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66926,10 +66926,10 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.405935674905777</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.7979603370092387</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67721,10 +67721,10 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.2191068232059479</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.7979603370092387</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68512,14 +68512,14 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.3180830776691437</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.7979603370092387</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69307,14 +69307,14 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.2360733449459076</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.05999134442239212</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70102,14 +70102,14 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>-0.000949859619140625</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.05999134442239218</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70897,14 +70897,14 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.4415966272354126</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.05999134442239218</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71692,14 +71692,14 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.4179934859275818</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.5979603370092387</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72491,10 +72491,10 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.3438968062400818</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.5979603370092387</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73286,10 +73286,10 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.2284430712461472</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.7979603370092387</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74081,10 +74081,10 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.2526485919952393</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.7979603370092387</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74876,10 +74876,10 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.2162156850099564</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.7979603370092387</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75667,14 +75667,14 @@
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.08964545279741287</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.7979603370092387</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76462,14 +76462,14 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.2433917671442032</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.7979603370092387</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77257,14 +77257,14 @@
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.3275987803936005</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.7979603370092387</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78052,14 +78052,14 @@
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.2463988661766052</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.7979603370092387</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78847,14 +78847,14 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.2318878620862961</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.7979603370092387</v>
+        <v>0.16</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79642,14 +79642,14 @@
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.2305437177419662</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.7979603370092387</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80437,14 +80437,14 @@
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.02081039920449257</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.7979603370092387</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81232,14 +81232,14 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.2263060659170151</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.7979603370092387</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82027,14 +82027,14 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.3238791823387146</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.7979603370092387</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82822,14 +82822,14 @@
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.2438395768404007</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.7979603370092387</v>
+        <v>0.3</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83617,14 +83617,14 @@
       </c>
       <c r="IZ104" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.2268029004335403</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.7979603370092387</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84416,10 +84416,10 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.3083260655403137</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.7979603370092387</v>
+        <v>-0.3</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85211,10 +85211,10 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.3530921936035156</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.7979603370092387</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86006,10 +86006,10 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.190089613199234</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.7979603370092387</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86797,14 +86797,14 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.2977668642997742</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.7979603370092387</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87592,14 +87592,14 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.1898956745862961</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.7979603370092387</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88387,14 +88387,14 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.1804720312356949</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.05999134442239212</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89186,10 +89186,10 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.02808487415313721</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.7179430258540229</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89981,10 +89981,10 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.01263512670993805</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.375894707285654</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90776,10 +90776,10 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.002393871545791626</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.7179430258540229</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91567,14 +91567,14 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.4039202630519867</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.05999134442239219</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92366,10 +92366,10 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.1479159891605377</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.5979603370092387</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93161,10 +93161,10 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.3405537605285645</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.7979603370092387</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93956,10 +93956,10 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.327836811542511</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.7979603370092387</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94751,10 +94751,10 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.3418741524219513</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.7979603370092387</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95542,14 +95542,14 @@
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.3336834013462067</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.1400086555776078</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96337,14 +96337,14 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.00154530256986618</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.5179430258540229</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97132,14 +97132,14 @@
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.01739969849586487</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.7179430258540229</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97931,10 +97931,10 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.3638637065887451</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.05999134442239229</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98722,14 +98722,14 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.369610071182251</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.5979603370092387</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99521,10 +99521,10 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.3114988207817078</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.7979603370092387</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100316,10 +100316,10 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.06390977650880814</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.7979603370092387</v>
+        <v>-0.5099999999999995</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101107,14 +101107,14 @@
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.03480565547943115</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.7979603370092387</v>
+        <v>0.3000000000000006</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/Attention-mamba2_repeat_2_000005.xlsx
+++ b/out/Attention-mamba2_repeat_2_000005.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>-0.2505265474319458</v>
+        <v>-0.2505437731742859</v>
       </c>
       <c r="JB2" t="n">
         <v>-1.28</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>-0.3352601230144501</v>
+        <v>-0.3352724611759186</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.9999999999999998</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>-0.2300024777650833</v>
+        <v>-0.2300183176994324</v>
       </c>
       <c r="JB4" t="n">
         <v>-0.7199999999999999</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>-0.2636118829250336</v>
+        <v>-0.2636339962482452</v>
       </c>
       <c r="JB5" t="n">
         <v>-0.4399999999999999</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>-0.1085541546344757</v>
+        <v>-0.1085634380578995</v>
       </c>
       <c r="JB6" t="n">
         <v>-0.4399999999999999</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>-0.1176963448524475</v>
+        <v>-0.1177081242203712</v>
       </c>
       <c r="JB7" t="n">
         <v>-0.16</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>-0.197364404797554</v>
+        <v>-0.1973536610603333</v>
       </c>
       <c r="JB8" t="n">
         <v>0.7199999999999999</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>-0.09499486535787582</v>
+        <v>-0.09499813616275787</v>
       </c>
       <c r="JB9" t="n">
         <v>0.7199999999999999</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>-0.02549728006124496</v>
+        <v>-0.025507852435112</v>
       </c>
       <c r="JB10" t="n">
         <v>0.7199999999999999</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>-0.04874556511640549</v>
+        <v>-0.04875496029853821</v>
       </c>
       <c r="JB11" t="n">
         <v>0.9999999999999998</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>-0.03663502261042595</v>
+        <v>-0.0366472527384758</v>
       </c>
       <c r="JB12" t="n">
         <v>0.9999999999999998</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>-0.03518557548522949</v>
+        <v>-0.03519772365689278</v>
       </c>
       <c r="JB13" t="n">
         <v>0.8599999999999999</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>-0.01470459252595901</v>
+        <v>-0.01471861451864243</v>
       </c>
       <c r="JB14" t="n">
         <v>0.8599999999999999</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>-0.03903701156377792</v>
+        <v>-0.03905004262924194</v>
       </c>
       <c r="JB15" t="n">
         <v>0.5799999999999998</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>-0.04322099685668945</v>
+        <v>-0.04323837533593178</v>
       </c>
       <c r="JB16" t="n">
         <v>-0.3</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>-0.2502374649047852</v>
+        <v>-0.2502057552337646</v>
       </c>
       <c r="JB17" t="n">
         <v>-0.5799999999999998</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>-0.2092070430517197</v>
+        <v>-0.2091884613037109</v>
       </c>
       <c r="JB18" t="n">
         <v>-0.7199999999999999</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>-0.4126845598220825</v>
+        <v>-0.4125683903694153</v>
       </c>
       <c r="JB19" t="n">
         <v>-0.9999999999999998</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>-0.3702339231967926</v>
+        <v>-0.370165079832077</v>
       </c>
       <c r="JB20" t="n">
         <v>-0.9999999999999998</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>-0.3430816829204559</v>
+        <v>-0.3429594337940216</v>
       </c>
       <c r="JB21" t="n">
         <v>-0.9999999999999998</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>-0.4450112581253052</v>
+        <v>-0.4449101984500885</v>
       </c>
       <c r="JB22" t="n">
         <v>-0.7199999999999999</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>-0.3133969306945801</v>
+        <v>-0.3100614547729492</v>
       </c>
       <c r="JB23" t="n">
         <v>-0.4399999999999999</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0.04055844247341156</v>
+        <v>0.04043693840503693</v>
       </c>
       <c r="JB24" t="n">
         <v>0.4399999999999999</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>-0.07518091797828674</v>
+        <v>-0.06040618196129799</v>
       </c>
       <c r="JB25" t="n">
         <v>0.7199999999999999</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0.04308973252773285</v>
+        <v>0.04296758770942688</v>
       </c>
       <c r="JB26" t="n">
         <v>0.7199999999999999</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0.02594505250453949</v>
+        <v>0.027581587433815</v>
       </c>
       <c r="JB27" t="n">
         <v>0.7199999999999999</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>-0.1699343621730804</v>
+        <v>-0.1702870875597</v>
       </c>
       <c r="JB28" t="n">
         <v>0.7199999999999999</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0.0428541898727417</v>
+        <v>0.04276787489652634</v>
       </c>
       <c r="JB29" t="n">
         <v>0.5799999999999998</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0.02365453541278839</v>
+        <v>0.02605222165584564</v>
       </c>
       <c r="JB30" t="n">
         <v>0.3</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>-0.02728001400828362</v>
+        <v>-0.01825536042451859</v>
       </c>
       <c r="JB31" t="n">
         <v>-0.3</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>-0.3192705512046814</v>
+        <v>-0.3191125988960266</v>
       </c>
       <c r="JB32" t="n">
         <v>-0.5799999999999998</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>-0.413053035736084</v>
+        <v>-0.4130163788795471</v>
       </c>
       <c r="JB33" t="n">
         <v>-0.7199999999999999</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>-0.4840645492076874</v>
+        <v>-0.4850833714008331</v>
       </c>
       <c r="JB34" t="n">
         <v>-0.5799999999999998</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0.001906275749206543</v>
+        <v>0.00177476555109024</v>
       </c>
       <c r="JB35" t="n">
         <v>-0.3</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0.06062937527894974</v>
+        <v>0.0604960098862648</v>
       </c>
       <c r="JB36" t="n">
         <v>-0.02000000000000007</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>-0.05491506308317184</v>
+        <v>-0.05429499968886375</v>
       </c>
       <c r="JB37" t="n">
         <v>0.8599999999999999</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0.03889298439025879</v>
+        <v>0.03876232355833054</v>
       </c>
       <c r="JB38" t="n">
         <v>0.9999999999999998</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0.04870113730430603</v>
+        <v>0.04855868965387344</v>
       </c>
       <c r="JB39" t="n">
         <v>0.8599999999999999</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0.03293269872665405</v>
+        <v>0.03278473019599915</v>
       </c>
       <c r="JB40" t="n">
         <v>0.8599999999999999</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0.03771161288022995</v>
+        <v>0.03757050633430481</v>
       </c>
       <c r="JB41" t="n">
         <v>0.8599999999999999</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0.01879118382930756</v>
+        <v>0.01864290982484818</v>
       </c>
       <c r="JB42" t="n">
         <v>0.7199999999999999</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0.04348297417163849</v>
+        <v>0.04334182292222977</v>
       </c>
       <c r="JB43" t="n">
         <v>0.7199999999999999</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0.04798171669244766</v>
+        <v>0.04784140735864639</v>
       </c>
       <c r="JB44" t="n">
         <v>0.8599999999999999</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0.03686877340078354</v>
+        <v>0.03671078383922577</v>
       </c>
       <c r="JB45" t="n">
         <v>0.2599999999999998</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0.0449666753411293</v>
+        <v>0.04482601583003998</v>
       </c>
       <c r="JB46" t="n">
         <v>0.1199999999999999</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0.04705824702978134</v>
+        <v>0.04691143333911896</v>
       </c>
       <c r="JB47" t="n">
         <v>0.2599999999999998</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0.03792746365070343</v>
+        <v>0.03777399659156799</v>
       </c>
       <c r="JB48" t="n">
         <v>0.2599999999999998</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0.04934027791023254</v>
+        <v>0.04920163750648499</v>
       </c>
       <c r="JB49" t="n">
         <v>0.8599999999999999</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0.03827935457229614</v>
+        <v>0.03813008964061737</v>
       </c>
       <c r="JB50" t="n">
         <v>0.7199999999999999</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0.04643064737319946</v>
+        <v>0.04629513621330261</v>
       </c>
       <c r="JB51" t="n">
         <v>0.8599999999999999</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0.03216800093650818</v>
+        <v>0.03201892971992493</v>
       </c>
       <c r="JB52" t="n">
         <v>0.1199999999999999</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0.04327747225761414</v>
+        <v>0.04313454031944275</v>
       </c>
       <c r="JB53" t="n">
         <v>-0.02000000000000007</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0.04913093149662018</v>
+        <v>0.04898776113986969</v>
       </c>
       <c r="JB54" t="n">
         <v>-0.02000000000000007</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0.02941092103719711</v>
+        <v>0.02925606071949005</v>
       </c>
       <c r="JB55" t="n">
         <v>-0.16</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0.05405247211456299</v>
+        <v>0.05391474068164825</v>
       </c>
       <c r="JB56" t="n">
         <v>-0.3</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>-0.103893481194973</v>
+        <v>-0.09459353238344193</v>
       </c>
       <c r="JB57" t="n">
         <v>-0.3</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0.03998608887195587</v>
+        <v>0.03985462337732315</v>
       </c>
       <c r="JB58" t="n">
         <v>-0.16</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0.01781599223613739</v>
+        <v>0.01767051219940186</v>
       </c>
       <c r="JB59" t="n">
         <v>-0.16</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0.03259295225143433</v>
+        <v>0.03243726491928101</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.02000000000000007</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0.0571846216917038</v>
+        <v>0.05704085528850555</v>
       </c>
       <c r="JB61" t="n">
         <v>0.7199999999999999</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0.004745960235595703</v>
+        <v>0.004591405391693115</v>
       </c>
       <c r="JB62" t="n">
         <v>0.8599999999999999</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0.04522063583135605</v>
+        <v>0.04508931934833527</v>
       </c>
       <c r="JB63" t="n">
         <v>0.7199999999999999</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0.04015333205461502</v>
+        <v>0.04000522196292877</v>
       </c>
       <c r="JB64" t="n">
         <v>0.5799999999999998</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0.03893821686506271</v>
+        <v>0.03879613429307938</v>
       </c>
       <c r="JB65" t="n">
         <v>0.5799999999999998</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0.04288101941347122</v>
+        <v>0.04274451732635498</v>
       </c>
       <c r="JB66" t="n">
         <v>-0.16</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0.04063998907804489</v>
+        <v>0.04048515111207962</v>
       </c>
       <c r="JB67" t="n">
         <v>-0.16</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0.04287440329790115</v>
+        <v>0.04273083806037903</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.16</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0.0464266911149025</v>
+        <v>0.04628531634807587</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.16</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0.04280437529087067</v>
+        <v>0.04265565425157547</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.02000000000000007</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0.04207804799079895</v>
+        <v>0.04193315654993057</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.02000000000000007</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0.04846125096082687</v>
+        <v>0.0483347475528717</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.3</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0.0273762047290802</v>
+        <v>0.02722106128931046</v>
       </c>
       <c r="JB73" t="n">
         <v>-0.4399999999999999</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>-0.423413097858429</v>
+        <v>-0.4233062565326691</v>
       </c>
       <c r="JB74" t="n">
         <v>-0.5799999999999998</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>-0.425064891576767</v>
+        <v>-0.4250036478042603</v>
       </c>
       <c r="JB75" t="n">
         <v>-0.8599999999999999</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>-0.4135252237319946</v>
+        <v>-0.413407027721405</v>
       </c>
       <c r="JB76" t="n">
         <v>-0.9999999999999998</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>-0.4389397799968719</v>
+        <v>-0.4388463199138641</v>
       </c>
       <c r="JB77" t="n">
         <v>-0.9999999999999998</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>-0.4556145370006561</v>
+        <v>-0.4555430114269257</v>
       </c>
       <c r="JB78" t="n">
         <v>-0.9999999999999998</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>-0.302689790725708</v>
+        <v>-0.3028499186038971</v>
       </c>
       <c r="JB79" t="n">
         <v>-0.9999999999999998</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>-0.2675372958183289</v>
+        <v>-0.2690216302871704</v>
       </c>
       <c r="JB80" t="n">
         <v>-0.9999999999999998</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>-0.2548133730888367</v>
+        <v>-0.2580122351646423</v>
       </c>
       <c r="JB81" t="n">
         <v>-0.9999999999999998</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>-0.3033689856529236</v>
+        <v>-0.303483635187149</v>
       </c>
       <c r="JB82" t="n">
         <v>-0.9999999999999998</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>-0.405935674905777</v>
+        <v>-0.4058894515037537</v>
       </c>
       <c r="JB83" t="n">
         <v>-0.9999999999999998</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>-0.2191068232059479</v>
+        <v>-0.2051056325435638</v>
       </c>
       <c r="JB84" t="n">
         <v>-0.9999999999999998</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>-0.3180830776691437</v>
+        <v>-0.3181011378765106</v>
       </c>
       <c r="JB85" t="n">
         <v>-0.1199999999999999</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>-0.2360733449459076</v>
+        <v>-0.2411870509386063</v>
       </c>
       <c r="JB86" t="n">
         <v>-0.1199999999999999</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>-0.000949859619140625</v>
+        <v>0.004130624234676361</v>
       </c>
       <c r="JB87" t="n">
         <v>-0.1199999999999999</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>-0.4415966272354126</v>
+        <v>-0.4415138363838196</v>
       </c>
       <c r="JB88" t="n">
         <v>-0.1199999999999999</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>-0.4179934859275818</v>
+        <v>-0.4179453253746033</v>
       </c>
       <c r="JB89" t="n">
         <v>-0.1199999999999999</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>-0.3438968062400818</v>
+        <v>-0.3439100086688995</v>
       </c>
       <c r="JB90" t="n">
         <v>-0.3999999999999999</v>
@@ -73286,10 +73286,10 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>-0.2284430712461472</v>
+        <v>-0.2069666981697083</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.9999999999999998</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74081,10 +74081,10 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>-0.2526485919952393</v>
+        <v>-0.256457656621933</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74872,14 +74872,14 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>-0.2162156850099564</v>
+        <v>-0.1955652832984924</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.7199999999999999</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75671,10 +75671,10 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>-0.08964545279741287</v>
+        <v>-0.04242713004350662</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.1199999999999999</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76466,10 +76466,10 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>-0.2433917671442032</v>
+        <v>-0.2457974255084991</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.1199999999999999</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>-0.3275987803936005</v>
+        <v>-0.3276089131832123</v>
       </c>
       <c r="JB96" t="n">
         <v>0.02000000000000007</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>-0.2463988661766052</v>
+        <v>-0.250007152557373</v>
       </c>
       <c r="JB97" t="n">
         <v>-0.1199999999999999</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>-0.2318878620862961</v>
+        <v>-0.2390723079442978</v>
       </c>
       <c r="JB98" t="n">
         <v>0.16</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>-0.2305437177419662</v>
+        <v>-0.2381962090730667</v>
       </c>
       <c r="JB99" t="n">
         <v>0.4399999999999999</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>-0.02081039920449257</v>
+        <v>-0.001494314521551132</v>
       </c>
       <c r="JB100" t="n">
         <v>0.4399999999999999</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>-0.2263060659170151</v>
+        <v>-0.2306568324565887</v>
       </c>
       <c r="JB101" t="n">
         <v>0.4399999999999999</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>-0.3238791823387146</v>
+        <v>-0.3238801956176758</v>
       </c>
       <c r="JB102" t="n">
         <v>0.5799999999999998</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>-0.2438395768404007</v>
+        <v>-0.2467478513717651</v>
       </c>
       <c r="JB103" t="n">
         <v>0.3</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>-0.2268029004335403</v>
+        <v>-0.2323180884122849</v>
       </c>
       <c r="JB104" t="n">
         <v>0.02000000000000007</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>-0.3083260655403137</v>
+        <v>-0.3083604574203491</v>
       </c>
       <c r="JB105" t="n">
         <v>-0.3</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>-0.3530921936035156</v>
+        <v>-0.3530614674091339</v>
       </c>
       <c r="JB106" t="n">
         <v>-0.4399999999999999</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>-0.190089613199234</v>
+        <v>-0.1616534441709518</v>
       </c>
       <c r="JB107" t="n">
         <v>-0.4399999999999999</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>-0.2977668642997742</v>
+        <v>-0.2977907657623291</v>
       </c>
       <c r="JB108" t="n">
         <v>-0.1600000000000001</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>-0.1898956745862961</v>
+        <v>-0.1787944287061691</v>
       </c>
       <c r="JB109" t="n">
         <v>0.7199999999999999</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>-0.1804720312356949</v>
+        <v>-0.1902123838663101</v>
       </c>
       <c r="JB110" t="n">
         <v>0.7199999999999999</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0.02808487415313721</v>
+        <v>0.0320977196097374</v>
       </c>
       <c r="JB111" t="n">
         <v>0.9999999999999998</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0.01263512670993805</v>
+        <v>0.02326006442308426</v>
       </c>
       <c r="JB112" t="n">
         <v>0.7199999999999999</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0.002393871545791626</v>
+        <v>0.01161995530128479</v>
       </c>
       <c r="JB113" t="n">
         <v>0.7199999999999999</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>-0.4039202630519867</v>
+        <v>-0.4037974178791046</v>
       </c>
       <c r="JB114" t="n">
         <v>0.4399999999999999</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>-0.1479159891605377</v>
+        <v>-0.1518325656652451</v>
       </c>
       <c r="JB115" t="n">
         <v>-0.4399999999999999</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>-0.3405537605285645</v>
+        <v>-0.3404231071472168</v>
       </c>
       <c r="JB116" t="n">
         <v>-0.7199999999999999</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>-0.327836811542511</v>
+        <v>-0.3277359008789062</v>
       </c>
       <c r="JB117" t="n">
         <v>-0.7199999999999999</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>-0.3418741524219513</v>
+        <v>-0.3417543470859528</v>
       </c>
       <c r="JB118" t="n">
         <v>-0.7199999999999999</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>-0.3336834013462067</v>
+        <v>-0.3336068987846375</v>
       </c>
       <c r="JB119" t="n">
         <v>-0.4399999999999999</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0.00154530256986618</v>
+        <v>0.01355483382940292</v>
       </c>
       <c r="JB120" t="n">
         <v>-0.4399999999999999</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0.01739969849586487</v>
+        <v>0.01962009817361832</v>
       </c>
       <c r="JB121" t="n">
         <v>-0.4399999999999999</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>-0.3638637065887451</v>
+        <v>-0.3637413680553436</v>
       </c>
       <c r="JB122" t="n">
         <v>-0.4399999999999999</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>-0.369610071182251</v>
+        <v>-0.3694795072078705</v>
       </c>
       <c r="JB123" t="n">
         <v>0.02000000000000007</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>-0.3114988207817078</v>
+        <v>-0.3113396763801575</v>
       </c>
       <c r="JB124" t="n">
         <v>-0.7199999999999999</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>-0.06390977650880814</v>
+        <v>-0.06398309022188187</v>
       </c>
       <c r="JB125" t="n">
         <v>-0.5099999999999995</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>-0.03480565547943115</v>
+        <v>-0.0349322110414505</v>
       </c>
       <c r="JB126" t="n">
         <v>0.3000000000000006</v>
